--- a/docs/StructureDefinition-internal-jugular-vein-pressure-observation.xlsx
+++ b/docs/StructureDefinition-internal-jugular-vein-pressure-observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-internal-jugular-vein-pressure-observation.xlsx
+++ b/docs/StructureDefinition-internal-jugular-vein-pressure-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2376" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2377" uniqueCount="513">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/internal-jugular-vein-pressure-observation</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/internal-jugular-vein-pressure-observation</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -471,7 +474,7 @@
     <t>gravityContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://mitre.org/fhir/space-health/StructureDefinition/gravity-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/gravity-context}
 </t>
   </si>
   <si>
@@ -491,7 +494,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -507,7 +510,7 @@
     <t>flightDay</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://mitre.org/fhir/space-health/StructureDefinition/flight-day}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/flight-day}
 </t>
   </si>
   <si>
@@ -745,7 +748,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://mitre.org/fhir/space-health/StructureDefinition/Astronaut)
+    <t xml:space="preserve">Reference(https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/astronaut)
 </t>
   </si>
   <si>
@@ -1877,54 +1880,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1982,149 +1987,149 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2136,16 +2141,16 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2195,31 +2200,31 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>20</v>
@@ -2230,10 +2235,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2241,10 +2246,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2253,19 +2258,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2315,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2350,10 +2355,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2361,10 +2366,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2373,16 +2378,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2433,19 +2438,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2468,10 +2473,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2479,31 +2484,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2553,19 +2558,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2588,10 +2593,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2599,10 +2604,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2614,16 +2619,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2649,13 +2654,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2673,19 +2678,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2708,21 +2713,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2734,16 +2739,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2793,19 +2798,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2817,7 +2822,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
@@ -2828,21 +2833,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2854,16 +2859,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2913,13 +2918,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2937,7 +2942,7 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
@@ -2948,10 +2953,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2959,10 +2964,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2974,13 +2979,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3019,29 +3024,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -3064,26 +3069,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -3092,13 +3097,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3149,19 +3154,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3184,26 +3189,26 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>20</v>
@@ -3212,13 +3217,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3269,19 +3274,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -3304,26 +3309,26 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -3332,13 +3337,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3389,19 +3394,19 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -3424,45 +3429,45 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3511,19 +3516,19 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
@@ -3535,7 +3540,7 @@
         <v>20</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>20</v>
@@ -3546,10 +3551,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3557,10 +3562,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3569,20 +3574,20 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3631,34 +3636,34 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>20</v>
@@ -3666,21 +3671,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3689,20 +3694,20 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3751,31 +3756,31 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>20</v>
@@ -3786,21 +3791,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3809,19 +3814,19 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3871,31 +3876,31 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>20</v>
@@ -3906,10 +3911,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3917,34 +3922,34 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3969,13 +3974,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3993,34 +3998,34 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>20</v>
@@ -4028,10 +4033,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4039,13 +4044,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
@@ -4054,19 +4059,19 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4091,13 +4096,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -4115,19 +4120,19 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -4139,10 +4144,10 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>20</v>
@@ -4150,45 +4155,45 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4213,13 +4218,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -4237,45 +4242,45 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4283,34 +4288,34 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4359,34 +4364,34 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>20</v>
@@ -4394,10 +4399,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4405,10 +4410,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4417,19 +4422,19 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4479,34 +4484,34 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>20</v>
@@ -4514,21 +4519,21 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4537,22 +4542,22 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4601,34 +4606,34 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>20</v>
@@ -4636,45 +4641,45 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4723,34 +4728,34 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4758,10 +4763,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4769,10 +4774,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4781,19 +4786,19 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4843,19 +4848,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -4864,13 +4869,13 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>20</v>
@@ -4878,10 +4883,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4889,10 +4894,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4901,20 +4906,20 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4963,34 +4968,34 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>20</v>
@@ -4998,10 +5003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5009,34 +5014,34 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5085,45 +5090,45 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5131,10 +5136,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -5146,13 +5151,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5203,13 +5208,13 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
@@ -5227,7 +5232,7 @@
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5238,21 +5243,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5264,16 +5269,16 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5311,31 +5316,31 @@
         <v>20</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -5347,7 +5352,7 @@
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -5358,10 +5363,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5369,10 +5374,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5381,22 +5386,22 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5445,19 +5450,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -5466,10 +5471,10 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5480,10 +5485,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5491,38 +5496,38 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>20</v>
@@ -5543,13 +5548,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5567,19 +5572,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5588,10 +5593,10 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -5602,10 +5607,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5613,10 +5618,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5625,20 +5630,20 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5687,19 +5692,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5708,10 +5713,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -5722,10 +5727,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5733,10 +5738,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5745,20 +5750,20 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5768,7 +5773,7 @@
         <v>20</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>20</v>
@@ -5807,19 +5812,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5828,10 +5833,10 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5842,10 +5847,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5853,10 +5858,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5865,22 +5870,22 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5890,7 +5895,7 @@
         <v>20</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>20</v>
@@ -5929,19 +5934,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -5950,10 +5955,10 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -5964,10 +5969,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5975,10 +5980,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5990,19 +5995,19 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6027,13 +6032,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -6051,19 +6056,19 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -6072,10 +6077,10 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6086,21 +6091,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -6112,19 +6117,19 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6149,13 +6154,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -6173,45 +6178,45 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6219,10 +6224,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6234,19 +6239,19 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6295,19 +6300,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6316,10 +6321,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6330,10 +6335,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6341,13 +6346,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
@@ -6356,16 +6361,16 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6391,13 +6396,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6415,45 +6420,45 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6461,10 +6466,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6476,19 +6481,19 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6513,13 +6518,13 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -6537,19 +6542,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6558,10 +6563,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6572,10 +6577,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6583,10 +6588,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6598,16 +6603,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6657,45 +6662,45 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6703,10 +6708,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6718,16 +6723,16 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6777,45 +6782,45 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6823,10 +6828,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6838,19 +6843,19 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6899,19 +6904,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -6920,10 +6925,10 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -6934,10 +6939,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6945,10 +6950,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6960,13 +6965,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7017,13 +7022,13 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
@@ -7041,7 +7046,7 @@
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7052,21 +7057,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -7078,16 +7083,16 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7137,19 +7142,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -7161,7 +7166,7 @@
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7172,45 +7177,45 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7259,19 +7264,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7283,7 +7288,7 @@
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7294,10 +7299,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7305,10 +7310,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7320,13 +7325,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7377,19 +7382,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7398,10 +7403,10 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7412,10 +7417,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7423,10 +7428,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7438,13 +7443,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7495,19 +7500,19 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7516,10 +7521,10 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7530,10 +7535,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7541,10 +7546,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7556,19 +7561,19 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7593,13 +7598,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7617,31 +7622,31 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7652,10 +7657,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7663,10 +7668,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7678,19 +7683,19 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7715,13 +7720,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7739,31 +7744,31 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AG48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>453</v>
-      </c>
       <c r="AN48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -7774,10 +7779,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7785,10 +7790,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7800,17 +7805,17 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7859,19 +7864,19 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -7883,7 +7888,7 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -7894,10 +7899,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7905,10 +7910,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7920,13 +7925,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7977,19 +7982,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -7998,10 +8003,10 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -8012,10 +8017,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8023,10 +8028,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -8035,19 +8040,19 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8097,19 +8102,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -8118,10 +8123,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8132,10 +8137,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8143,10 +8148,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8155,19 +8160,19 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8217,19 +8222,19 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -8238,10 +8243,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8252,10 +8257,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8263,10 +8268,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -8275,22 +8280,22 @@
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8339,19 +8344,19 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -8360,10 +8365,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8374,10 +8379,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8385,10 +8390,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8400,13 +8405,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8457,13 +8462,13 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
@@ -8481,7 +8486,7 @@
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8492,21 +8497,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8518,16 +8523,16 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8577,19 +8582,19 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8601,7 +8606,7 @@
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8612,45 +8617,45 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8699,19 +8704,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8723,7 +8728,7 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8734,10 +8739,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8745,10 +8750,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8757,22 +8762,22 @@
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8797,13 +8802,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8821,34 +8826,34 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>20</v>
@@ -8856,10 +8861,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8867,10 +8872,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -8879,22 +8884,22 @@
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -8943,45 +8948,45 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8989,10 +8994,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -9004,19 +9009,19 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9041,13 +9046,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -9065,19 +9070,19 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -9086,10 +9091,10 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9100,21 +9105,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9126,19 +9131,19 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9163,13 +9168,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9187,45 +9192,45 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9233,10 +9238,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -9248,19 +9253,19 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9309,19 +9314,19 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
@@ -9330,10 +9335,10 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
